--- a/resources/templates/standard/A1100-02.xlsx
+++ b/resources/templates/standard/A1100-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>(      )사업부 업무 분장 변경 신청서</t>
   </si>
@@ -551,12 +554,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.15" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -584,31 +589,31 @@
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
       <c r="AE1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF1" s="3"/>
       <c r="AG1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH1" s="4"/>
       <c r="AI1" s="4"/>
       <c r="AJ1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK1" s="4"/>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN1" s="4"/>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ1" s="4"/>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT1" s="4"/>
       <c r="AU1" s="4"/>
@@ -668,7 +673,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -683,7 +688,7 @@
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
@@ -717,7 +722,7 @@
     </row>
     <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -742,7 +747,7 @@
       <c r="V4" s="7"/>
       <c r="W4" s="7"/>
       <c r="X4" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y4" s="8"/>
       <c r="Z4" s="8"/>
@@ -819,7 +824,7 @@
     </row>
     <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -844,7 +849,7 @@
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
       <c r="X6" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y6" s="10"/>
       <c r="Z6" s="10"/>
@@ -1852,7 +1857,7 @@
     </row>
     <row r="27" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
